--- a/Analysis/clean data/Survey 1_scored_near complete_16.6.26.xlsx
+++ b/Analysis/clean data/Survey 1_scored_near complete_16.6.26.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D6">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D7">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="D8">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="D9">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D10">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D11">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D12">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D13">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D14">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D15">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D16">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D17">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D18">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D19">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D20">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D21">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D22">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D23">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D24">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D25">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D26">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D27">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D28">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D29">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D30">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D31">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D32">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="D33">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="D34">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="D35">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="D36">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="D37">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="D38">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="D39">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D40">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D41">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D42">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="D43">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="D44">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="D45">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="D46">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="D47">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="D48">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="D49">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D50">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D51">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="D52">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="D53">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="D54">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="D55">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="D56">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="D57">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="D58">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="D59">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="D60">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="D61">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="D62">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="D63">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="D64">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="D65">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="D66">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="D67">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="D68">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="D69">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="D70">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="D71">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R35</t>
         </is>
       </c>
       <c r="D72">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>R36</t>
         </is>
       </c>
       <c r="D73">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>R36</t>
         </is>
       </c>
       <c r="D74">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>R36</t>
         </is>
       </c>
       <c r="D75">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>R36</t>
+          <t>R37</t>
         </is>
       </c>
       <c r="D76">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>R37</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
